--- a/branches/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:58:53+00:00</t>
+    <t>2026-09-02T18:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:12:27+00:00</t>
+    <t>2026-09-02T20:19:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
